--- a/lucas/import_data/utility/landscape/excel/land_cover_family.xlsx
+++ b/lucas/import_data/utility/landscape/excel/land_cover_family.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="108">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -34,6 +34,9 @@
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">city/town area</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
     <t xml:space="preserve">City/town area</t>
   </si>
   <si>
+    <t xml:space="preserve">city-town</t>
+  </si>
+  <si>
     <t xml:space="preserve">other artificial areas</t>
   </si>
   <si>
@@ -55,6 +61,9 @@
     <t xml:space="preserve">Other artificial areas</t>
   </si>
   <si>
+    <t xml:space="preserve">artificial-other</t>
+  </si>
+  <si>
     <t xml:space="preserve">non-agricultural vegetated areas</t>
   </si>
   <si>
@@ -64,6 +73,9 @@
     <t xml:space="preserve">Non-agricultural vegetated areas</t>
   </si>
   <si>
+    <t xml:space="preserve">non-ag-veg</t>
+  </si>
+  <si>
     <t xml:space="preserve">cultivated cropland</t>
   </si>
   <si>
@@ -76,6 +88,9 @@
     <t xml:space="preserve">Cultivated cropland</t>
   </si>
   <si>
+    <t xml:space="preserve">cultivated</t>
+  </si>
+  <si>
     <t xml:space="preserve">agroforestry</t>
   </si>
   <si>
@@ -85,6 +100,9 @@
     <t xml:space="preserve">Agroforestry</t>
   </si>
   <si>
+    <t xml:space="preserve">agroforest</t>
+  </si>
+  <si>
     <t xml:space="preserve">broadleaved woodland</t>
   </si>
   <si>
@@ -97,6 +115,9 @@
     <t xml:space="preserve">Broadleaved woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">broadl-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">coniferous woodland</t>
   </si>
   <si>
@@ -106,6 +127,9 @@
     <t xml:space="preserve">Coniferous woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">conif-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">mixed woodland</t>
   </si>
   <si>
@@ -115,6 +139,9 @@
     <t xml:space="preserve">Mixed woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">mixed-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">coppice and coppice with standards</t>
   </si>
   <si>
@@ -124,6 +151,9 @@
     <t xml:space="preserve">Coppice and coppice with standards</t>
   </si>
   <si>
+    <t xml:space="preserve">coppice</t>
+  </si>
+  <si>
     <t xml:space="preserve">felling</t>
   </si>
   <si>
@@ -145,6 +175,9 @@
     <t xml:space="preserve">Shrubland with sparse tree cover</t>
   </si>
   <si>
+    <t xml:space="preserve">shrub-l-trees</t>
+  </si>
+  <si>
     <t xml:space="preserve">shrubland without tree cover</t>
   </si>
   <si>
@@ -154,6 +187,9 @@
     <t xml:space="preserve">Shrubland without tree cover</t>
   </si>
   <si>
+    <t xml:space="preserve">shrub-l-no-trees</t>
+  </si>
+  <si>
     <t xml:space="preserve">grassland with sparse tree/shrub cover</t>
   </si>
   <si>
@@ -166,6 +202,9 @@
     <t xml:space="preserve">Grassland with sparse tree/shrub cover</t>
   </si>
   <si>
+    <t xml:space="preserve">grass-l-trees</t>
+  </si>
+  <si>
     <t xml:space="preserve">grassland without tree/shrub cover</t>
   </si>
   <si>
@@ -175,6 +214,9 @@
     <t xml:space="preserve">Grassland without tree/shrub cover</t>
   </si>
   <si>
+    <t xml:space="preserve">grass-l-no-trees</t>
+  </si>
+  <si>
     <t xml:space="preserve">spontaneous vegetation</t>
   </si>
   <si>
@@ -184,6 +226,9 @@
     <t xml:space="preserve">Spontaneous vegetation</t>
   </si>
   <si>
+    <t xml:space="preserve">spontan</t>
+  </si>
+  <si>
     <t xml:space="preserve">bare land and lichens/moss</t>
   </si>
   <si>
@@ -196,6 +241,9 @@
     <t xml:space="preserve">Bare land and lichens/moss</t>
   </si>
   <si>
+    <t xml:space="preserve">bare-lich-mss</t>
+  </si>
+  <si>
     <t xml:space="preserve">rocks</t>
   </si>
   <si>
@@ -205,6 +253,9 @@
     <t xml:space="preserve">Rocks</t>
   </si>
   <si>
+    <t xml:space="preserve">rock</t>
+  </si>
+  <si>
     <t xml:space="preserve">sand and stone</t>
   </si>
   <si>
@@ -214,6 +265,9 @@
     <t xml:space="preserve">Sand and stone</t>
   </si>
   <si>
+    <t xml:space="preserve">sand-stone</t>
+  </si>
+  <si>
     <t xml:space="preserve">other bare soil</t>
   </si>
   <si>
@@ -223,6 +277,9 @@
     <t xml:space="preserve">Other bare soil</t>
   </si>
   <si>
+    <t xml:space="preserve">bare-other</t>
+  </si>
+  <si>
     <t xml:space="preserve">lichens</t>
   </si>
   <si>
@@ -253,6 +310,9 @@
     <t xml:space="preserve">Inland water bodies</t>
   </si>
   <si>
+    <t xml:space="preserve">lake</t>
+  </si>
+  <si>
     <t xml:space="preserve">inland running water</t>
   </si>
   <si>
@@ -262,12 +322,18 @@
     <t xml:space="preserve">Inland running water</t>
   </si>
   <si>
+    <t xml:space="preserve">stream</t>
+  </si>
+  <si>
     <t xml:space="preserve">g30</t>
   </si>
   <si>
     <t xml:space="preserve">Coastal water</t>
   </si>
   <si>
+    <t xml:space="preserve">coastal</t>
+  </si>
+  <si>
     <t xml:space="preserve">wetland</t>
   </si>
   <si>
@@ -275,6 +341,9 @@
   </si>
   <si>
     <t xml:space="preserve">Swamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swamp</t>
   </si>
 </sst>
 </file>
@@ -284,7 +353,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -305,11 +374,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -359,11 +423,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -490,7 +554,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.48"/>
@@ -512,355 +576,433 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>72</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>76</v>
+        <v>95</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>84</v>
+        <v>106</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
